--- a/Pedidos_Manutencao.xlsx
+++ b/Pedidos_Manutencao.xlsx
@@ -4146,7 +4146,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3913 - CARGA TEXTIL IND.E COM.DE EQUIP.DE MOV.MODAL EIRELI EPP</t>
+          <t>3913 - CARGA TEXTIL IND.E COM.DE EQUIP.DE MOV.MODAL LTDA.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/Pedidos_Manutencao.xlsx
+++ b/Pedidos_Manutencao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W80"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,59 +539,167 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3MI INDUCAO - SC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12.563.613/0002-05</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8549</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>14242</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2643 - SRC MOLAS INDUSTRIAIS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2643 - INDUSTRIA E COMERCIO DE MOLAS SRC LTDA.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SP - MANUTENÇÃO PREVENTIVA</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EM EXECUCAO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTO:
+EQUIPAMENTO AQUECIMENTO INDUTIVO FORJA MANUAL 25 E 60KW - TROCADOR DE CALOR
+REALIZACAO DE MANUTENCAO PREVENTIVA
+DEFEITO:
+CONFORME SUJERIDO AO CLIENTE OFERTAMOS UMA MANUTENCAO PREVENTIVA DO EQUIPAMENTO ACIMA DE NOSSA FABRICACAO. O QUAL ALEM DE TODOS ITENS PREVISTOS EM NOSSO CHECK LIST ANEXO, CASO SEJA NECESSARIO SUBSTITUIREMOS FILTROS E CONECTORES.
+NESTE VALOR NAO ESTAO INCLUSOS PECAS E COMPONENTES CASO SEJA NECESSARIO A SUBSTITUICAO, CASO SEJA VERIFICADO A NECESSIDADE ENVIAREMOS ORCAMENTO COMPLEMENTAR O QUAL SOMENTE DAREMOS SEQUENCIA MEDIANTE A SUA APROVACAO.
+PRAZO PARA EXECUCAO DO SERVICO 01 DIA UTIL .(POR EQUIPAMENTO)
+CASO AUTORIZE A EXECUCAO DO SERVICO PEDIMOS QUE NOS INFORME COM PELO MENOS 5 DIAS DE ANTECEDENCIA PARA PROVIDENCIAR-MOS O MATERIAL NECESSARIO E ENCAIXARMOS NA AGENDA DOS TECNICOS.
+O VALOR APRESENTADO TRATA-SE DE APENAS 1 EQUIPAMENTO
+LAUDO/OBS.:
+SERVIÇO REALIZADO EM 17/9 PELOS TECNICOS VINIVIUS E ISAC
+EQUIPAMENTO EM OPERAÇÃO
+VIDE RELATORIO ANEXO
+COR: 
+SERVICOS:
+1341 - SERVICOS PRESTADOS DIVERSOS
+QTD.: 1,000 UN
+PRODUTOS:
+12116 - PINO CONEC. ENGATE RAPIDO 1/2C/R.M 1/2 LATAO
+QTD.: 2,000 UN
+165 - MANGUEIRA NAO CONDUTIVA 1/2 PRETA
+QTD.: 6,000 M</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>SERGIO PRATES PEREIRA</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>3210</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>588.53000000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>3798.53</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>46267</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>8496</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>13782</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 120KW - 380V FREQUENCIA 15-30KHZ
@@ -609,89 +717,89 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="R3" t="n">
         <v>5932</v>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
         <v>5932</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
         <is>
           <t>5932.00000000</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>8466</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>9631</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1703 - FORJARIA E SERRALHERIA MOREIRA LTDA. ME</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1703 - FORJARIA E SERRALHERIA MOREIRA LTDA. ME</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO POR INDUCAO MANUAL 25KW - 380V FREQUENCIA 15-30KHZ FABRICACAO/MARCA: 3MI
@@ -709,89 +817,89 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>4980</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>4980</v>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
         <is>
           <t>4980.00000000</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>7904</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>13086</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>4111 - MOTOPPAR</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>4111 - MOTOPPAR IND COM DE AUTOMATIZADORES LTDA</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENÇÃO PREVENTIVA EM EQUIPAMENTOS DE TEMPERA POR INDUÇÃO 40KW TENSA0 380V FREQUENCIA 15-27KHZ
@@ -815,93 +923,93 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>10319.04</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="n">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>10319.04</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>10319.04000000</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="6">
+      <c r="A6" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>7836</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>12727.1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE AQUECIMENTO POR INDUÇÃO 40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -923,93 +1031,93 @@
 QTD.:</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>9790</v>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
         <v>9790</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>9790.00000000</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    <row r="7">
+      <c r="A7" s="1" t="n">
         <v>46035</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>7699</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>12622</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENÇÃO REALIZADA EQUIPAMENTO FORJARIA 160KW TENSAO 380V FREQUENCIA 15-26KHZ
@@ -1040,105 +1148,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>6428-1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>2427.32</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>746.50000000</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
         <v>3173.82</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>3173.82000000</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    <row r="8">
+      <c r="A8" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>7605</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>12222</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO PNEUMATICO - 40KW 380V FREQUENCIA 15-30KHZ
@@ -1155,93 +1263,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-01-08</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>4836</v>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="n">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
         <v>4836</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>4836.00000000</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    <row r="9">
+      <c r="A9" s="1" t="n">
         <v>46001</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>7639</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>6215</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>736 - METALFLEXO</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>736 - METALFLEXO IND.COM.FER.FLEXOGRAFIA LTDA</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA TEMPERA - POTENCIA 40KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -1255,93 +1363,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2025-12-17</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>5395.2</v>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
         <v>5395.2</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>5395.20000000</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+    <row r="10">
+      <c r="A10" s="1" t="n">
         <v>45979</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>7554</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>11947</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>7069 - ZANINI RENK</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>7069 - ZANINI RENK EQUIPAMENTOS INDUSTRIAIS LTDA</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE AQUECIMENTO POR INDUÇÃO PARA MONTAGENS DE ROLAMENTOS POR DILATAÇÃO TERMICO MARCA JAMO
@@ -1367,105 +1475,105 @@
 QTD.: 1,000 UNID</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>5688-1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1939.42</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>3262.00000000</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
         <v>5201.42</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>5201.42000000</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    <row r="11">
+      <c r="A11" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>7374</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>12053</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI/JAMO - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -1487,93 +1595,93 @@
 QTD.: 3,000 UN</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>12600</v>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="n">
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>12600</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>12600.00000000</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>7373</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>12230</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI/JAMO - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -1595,93 +1703,93 @@
 QTD.: 3,000 UN</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>8400</v>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="n">
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
         <v>8400</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>8400.00000000</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    <row r="13">
+      <c r="A13" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>7270</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>12067</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 PEÇAS PARA SER SUBSTITUIDA EM MANUTENÇÃO PREVENTIVA DE EQUIPAMENTO
@@ -1694,105 +1802,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>6038-1</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>4460.40000000</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
         <v>4460.4</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>4460.40000000</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="14">
+      <c r="A14" s="1" t="n">
         <v>45909</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>7254</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>12054</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI/JAMO - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -1813,93 +1921,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>5690</v>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="n">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
         <v>5690</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>5690.00000000</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    <row r="15">
+      <c r="A15" s="1" t="n">
         <v>45896</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>7202</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>11935</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM UM EQUIPAMENTO MARCA JAMO AQUECIMENTO CONTINUO DE FIO MAQUINA
@@ -1929,89 +2037,89 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>5339.6</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>4460.40000000</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
         <v>9800</v>
       </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    <row r="16">
+      <c r="A16" s="1" t="n">
         <v>45859</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>7055</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>11783</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2472 - FIXABEM SERVICOS DE FERRAGENS E FERRAMENTAS LTDA.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2472 - FIXA BEM SERVICOS DE FERRAGENS E FERRAMENTAS LTDA</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENÇÃO PREVENTIVA EM EQUIPAMENTOS DE FORJA MANUAL MARCA JAMO - 80 KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -2027,93 +2135,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>6140</v>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="n">
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
         <v>6140</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>6140.00000000</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    <row r="17">
+      <c r="A17" s="1" t="n">
         <v>45833</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>6908</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>11625</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 25KW FREQUENCIA 15-30KHZ 380V - MARCA JAMO SERIE E05911
@@ -2129,93 +2237,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>4390</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
         <v>4390</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>4390.00000000</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    <row r="18">
+      <c r="A18" s="1" t="n">
         <v>45839</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>6959</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>11663</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA MANUAL 60KW TENSAO 380V FREQUENCIA 15-30KHZ MARCA JAMO
@@ -2228,105 +2336,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>5732-1</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>3603.42000000</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
         <v>3603.42</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>3603.43000000</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>11649</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 CONFORME SOLICITADO PELO SR. MANOEL EM JÁ PRÉ AGENDADO PARA EXECUTARMOS EM 01/07/2025, MANUTENÇÃO PREVENTIVA NO EQUIPAMENTO FORJA MANUAL 60KW NUMERO DE SERIE E-03788
@@ -2362,97 +2470,97 @@
 QTD.: 22,000 UN</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>2610.26</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>2662.56000000</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
         <v>5272.82</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>5272.82000000</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    <row r="20">
+      <c r="A20" s="1" t="n">
         <v>45812</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>6833</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>11286</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>4859 - LORD FERRAMENTAS</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>4859 - LORD EZEQUIEL INDUSTRIA E COMERCIO DE FERRAMENTAS LTDA</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO POR INDUÇÃO 40KW TENSÃO 380V FREQUENCIA 15-27KHZ
@@ -2471,93 +2579,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>4600</v>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
         <v>4600</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>4600.00000000</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    <row r="21">
+      <c r="A21" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>6841</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>11481</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 CONFORME SOLICITADO PELO SR. MANOEL PRODUÇÃO BRASIMPAR REALIZAMOS UMA MANUTENÇÃO PREVENTIVA NO EQUIPAMENTO FORJA MANUAL 40KW NUMERO DE SERIE E-03381/5
@@ -2594,105 +2702,105 @@
 QTD.: 1,500 M</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
         <is>
           <t>5642-1</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>2222.06</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2059.31000000</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="n">
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
         <v>4281.37</v>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>4281.38000000</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>45754</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>6648</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>11219</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA AUTOMATICA - 3MI - 100KW TENSAO 380V FREQUENCIA 15-30 KHZ
@@ -2740,105 +2848,105 @@
 QTD.: 3,000 PC</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
         <is>
           <t>5425-1</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>2425.6</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>7562.19000000</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
         <v>9987.790000000001</v>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>9987.79000000</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+    <row r="23">
+      <c r="A23" s="1" t="n">
         <v>45744</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>6621</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>11181</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA - ME</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>DEFEITO:
 MANUTENCAO PREVENTIVA DE 4 MAQUINAS E 1 MAQUINA DE TEMPERA
@@ -2857,93 +2965,93 @@
 QTD.: 4,000 UN</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>8400</v>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="n">
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
         <v>8400</v>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>8400.00000000</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+    <row r="24">
+      <c r="A24" s="1" t="n">
         <v>45699</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>6456</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>10919</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE AQUECIMENTO POR INDUÇÃO 40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -2963,93 +3071,93 @@
 QTD.: 7,000 HR</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>10100</v>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="n">
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
         <v>10100</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>10100.00000000</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+    <row r="25">
+      <c r="A25" s="1" t="n">
         <v>45695</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>10907</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA NOS 3 EQUIPAMENTOS DE TEMPERA 3MI 
@@ -3072,93 +3180,93 @@
 QTD.: 16,000 HR</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>6845</v>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="n">
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
         <v>6845</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>6845.00000000</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+    <row r="26">
+      <c r="A26" s="1" t="n">
         <v>45680</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>6402</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>10816</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA FORJA - POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -3178,93 +3286,93 @@
 QTD.: 3,000 UN</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>2025-01-26</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>7787.2</v>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="n">
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
         <v>7787.2</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>7787.20000000</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    <row r="27">
+      <c r="A27" s="1" t="n">
         <v>45677</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>6382</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>7457</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>2612 - DYNAR AUTOMATIZACAO INDUSTRIAL LTDA</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2612 - DYNAR AUTOMATIZACAO INDUSTRIAL LTDA</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS SOLDA POR BRASAGEM - 10KW - TENSAO 380V
@@ -3282,93 +3390,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>2025-01-23</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>3680</v>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="n">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
         <v>3680</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>3680.00000000</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
+    <row r="28">
+      <c r="A28" s="1" t="n">
         <v>45644</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>6284</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>10559</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>203 - USINA DA PECA</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>203 - USINA DA PECA IND E COMERCIO DE PECAS E MAQ. AGRIC. LTDA</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TRATAMENTO TERMICO DUPLO 160KW TENSAO 380V - FREQUENCIA 15-30KHZ
@@ -3407,105 +3515,105 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>2024-12-21</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
         <is>
           <t>5112-1</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>7274.87</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>8225.12000000</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="n">
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
         <v>15499.99</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>15500.00000000</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
+    <row r="29">
+      <c r="A29" s="1" t="n">
         <v>45609</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>6146</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>10546</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA JAMO - POTENCIA 100KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -3520,89 +3628,89 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>4200</v>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="n">
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
         <v>4200</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>4200.00000000</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
+    <row r="30">
+      <c r="A30" s="1" t="n">
         <v>45604</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>6118</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -3623,93 +3731,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>4200</v>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="n">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
         <v>4200</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>4200.00000000</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    <row r="31">
+      <c r="A31" s="1" t="n">
         <v>45595</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>6077</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>9789</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA COM ALIMENTACAO PNEUMATICA - 25/40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -3731,105 +3839,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>5004-1</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>831.2</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>667.61000000</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="n">
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="n">
         <v>1498.81</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>1498.82000000</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    <row r="32">
+      <c r="A32" s="1" t="n">
         <v>45588</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>6030</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>10419</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU8 SEM - MARCA 3MI - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -3854,93 +3962,93 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2024-10-24</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>8400</v>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="n">
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="n">
         <v>8400</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>8400.00000000</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    <row r="33">
+      <c r="A33" s="1" t="n">
         <v>45583</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>6015</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>10342</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>981 - INDUSTRIAS GERAIS DE PARAFUSOS INGEPAL LTDA</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>981 - INDS.GERAIS DE PARAFUSOS INGEPAL LTDA</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO PNEUMATICO - 40KW / 100KW 380V FREQUENCIA 15-30KHZ
@@ -3957,93 +4065,93 @@
 VERIFICAR COM O CLIENTE SE JÁ QUER DEIXAR AGENDADO DATA PARA PROXIMA MAQUINA</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>4450</v>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="n">
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
         <v>4450</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>4450.00000000</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    <row r="34">
+      <c r="A34" s="1" t="n">
         <v>45575</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>5968</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>10305</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>1469 - MRS - IRMA CESTARI</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1469 - IND. E COM. DE PECAS MRS LTDA</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE TEMPERA POR INDUCAO DUPLO (HORIZONTAL E VERTICAL) 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4061,105 +4169,105 @@
 QTD.: 2,000 PC</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>4889-1</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>9540.30000000</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="n">
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="n">
         <v>9540.299999999999</v>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>9540.30000000</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
+    <row r="35">
+      <c r="A35" s="1" t="n">
         <v>45568</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>5927</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>10172</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>3913 - FITA CABO - CARGA TEXTIL</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>3913 - CARGA TEXTIL IND.E COM.DE EQUIP.DE MOV.MODAL LTDA.</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS COM CALHA MARCA 3MI - POTENCIA 40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4176,93 +4284,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>4452</v>
       </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="n">
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="n">
         <v>4452</v>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>4452.00000000</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="36">
+      <c r="A36" s="1" t="n">
         <v>45568</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>5928</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>10174</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU8 SEM - MARCA 3MI - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4287,93 +4395,93 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>8400</v>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="n">
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="n">
         <v>8400</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>8400.00000000</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="37">
+      <c r="A37" s="1" t="n">
         <v>45546</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>5805</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>10113</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MAQUINAS DE TEMPERA
@@ -4396,93 +4504,93 @@
 QTD.: 16,000 HR</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>7505</v>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="n">
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="n">
         <v>7505</v>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>7505.00000000</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    <row r="38">
+      <c r="A38" s="1" t="n">
         <v>45546</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>5808</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>9193</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>4049 - GAR AUTO PARTS</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>4049 - GAR IND. COM. DE PECAS AUTOMOTIVAS LTDA.</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA JAMO POTENCIA 100KW
@@ -4506,105 +4614,105 @@
 QTD.: 600,000 KM</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
         <is>
           <t>4809-1</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>3740</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>1688.65000000</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="n">
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
         <v>5428.65</v>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>5428.65000000</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    <row r="39">
+      <c r="A39" s="1" t="n">
         <v>45545</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>5804</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>10124</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI ME</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TEMPERA 60KW - TENSAO 380V
@@ -4620,105 +4728,105 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>4786-1</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>2168.25000000</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="n">
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="n">
         <v>2168.25</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>2168.26000000</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    <row r="40">
+      <c r="A40" s="1" t="n">
         <v>45538</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>5756</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>9854</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO TEMPERA POR INDUCAO CONTRA PONTA DUPLO POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -4740,93 +4848,93 @@
 AGENDADO PARA 05 E 06/09/24.</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R40" t="n">
         <v>9675.459999999999</v>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="n">
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="n">
         <v>9675.459999999999</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>9675.46000000</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    <row r="41">
+      <c r="A41" s="1" t="n">
         <v>45531</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>5714</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>9996</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TRATAMENTO TERMICO TEMPERA POR INDUCAO ENTRE PONTAS DUPLO - 160KW - 380V FREQUENCIA 15-30KHZ
@@ -4856,105 +4964,105 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
         <is>
           <t>4731-1</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>1543.6</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>6456.39000000</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="n">
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="n">
         <v>7999.99</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>8000.00000000</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    <row r="42">
+      <c r="A42" s="1" t="n">
         <v>45527</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>5698</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>8655</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>1469 - MRS - IRMA CESTARI</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>1469 - IND. E COM. DE PECAS MRS LTDA</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE TEMPERA POR INDUCAO DUPLO POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -4972,93 +5080,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>2024-08-26</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>7879.2</v>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="n">
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="n">
         <v>7879.2</v>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>7879.20000000</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    <row r="43">
+      <c r="A43" s="1" t="n">
         <v>45496</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>5554</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>9733</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>1390 - INOX PAR INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>1390 - INOX PAR INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO POR INDUCAO FORJA MANUAL 3MI - POTENCIA 25KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -5081,105 +5189,105 @@
 QTD.: 1,000 UND</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
         <is>
           <t>4649-1</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>5270</v>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>4429.43000000</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="n">
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="n">
         <v>9699.43</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>9699.43000000</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    <row r="44">
+      <c r="A44" s="1" t="n">
         <v>45491</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>5528</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>9806</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EQUIPAMENTO 60KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -5197,93 +5305,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>2024-07-19</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>4120</v>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="n">
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="n">
         <v>4120</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>4120.00000000</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    <row r="45">
+      <c r="A45" s="1" t="n">
         <v>45488</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>5507</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>9760</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>618 - PROSPAR INDUSTRIA E COMERCIO DE PARAFUSOS LTDA - EPP</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>618 - PROSPAR - IND COM PARAFUSOS LTDA</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA AUTOMATICA
@@ -5308,105 +5416,105 @@
 QTD.: 7,000 M</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
         <is>
           <t>4583-1</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>3080</v>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>1045.47000000</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="n">
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="n">
         <v>4125.47</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>4125.47000000</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    <row r="46">
+      <c r="A46" s="1" t="n">
         <v>45479</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>5468</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI ME</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIOPAMENTO TRATAMENTO TERMICO DUPLO EIXO - 60KW
@@ -5423,93 +5531,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>5300</v>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="n">
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
         <v>5300</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>5300.00000000</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="47">
+      <c r="A47" s="1" t="n">
         <v>45455</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>5367</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>9588</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>752 - PERFIL FACAS</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>752 - PERFIL INDUSTRIA DE FACAS ROTATIVAS LTDA - EPP</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA TEMPERA - POTENCIA 40KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -5523,93 +5631,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>2024-06-15</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>5000</v>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="n">
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
         <v>5000</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>5000.00000000</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    <row r="48">
+      <c r="A48" s="1" t="n">
         <v>45450</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>5343</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>9536</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO ALIMENTACAO MANUAL 
@@ -5627,93 +5735,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>4120</v>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="n">
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
         <v>4120</v>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>4120.00000000</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    <row r="49">
+      <c r="A49" s="1" t="n">
         <v>45441</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>5311</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>9516</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA MAQUINA 40KW - TENSAO 380V - FREQUENCIA 15-30KHZ
@@ -5723,93 +5831,93 @@
 QTD.: 3.600,000 UN</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R49" t="n">
         <v>3600</v>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="n">
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="n">
         <v>3600</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>3600.00000000</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
+    <row r="50">
+      <c r="A50" s="1" t="n">
         <v>45432</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>5246</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>9183</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA AUTOMATICA 
@@ -5841,105 +5949,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>2024-05-23</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>4410-1</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R50" t="n">
         <v>1733.6</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>3736.95000000</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="n">
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="n">
         <v>5470.55</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>5470.55000000</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
+    <row r="51">
+      <c r="A51" s="1" t="n">
         <v>45412</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>5169</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>9297.1</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE TEMPRAS
@@ -5972,105 +6080,105 @@
 QTD.: 16,000 M</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>2024-05-20</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
         <is>
           <t>4454-1</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="R51" t="n">
         <v>11405</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>4749.67000000</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="n">
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="n">
         <v>16154.67</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>16154.68000000</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
+    <row r="52">
+      <c r="A52" s="1" t="n">
         <v>45429</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>5244</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>9362</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>2968 - VAZ VAZ METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>2968 - VAZ E VAZ METALURGICA LTDA ME</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>DEFEITO:
 EQUIPAMENTO COM FALHA DE ALTA CORRENTE
@@ -6095,105 +6203,105 @@
 QTD.: 6,000 PC</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
         <is>
           <t>4406-1</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="R52" t="n">
         <v>4519.71</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>2874.48000000</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="n">
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="n">
         <v>7394.19</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>7394.20000000</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
+    <row r="53">
+      <c r="A53" s="1" t="n">
         <v>45412</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>5168</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>9271</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA AUTOMATICA M160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -6216,105 +6324,105 @@
 QTD.: 2,000 PC</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>2024-05-03</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
         <is>
           <t>4348-1</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R52" t="n">
+      <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>7791.25000000</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="n">
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="n">
         <v>7791.25</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>7791.25000000</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
+    <row r="54">
+      <c r="A54" s="1" t="n">
         <v>45404</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>5130</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>9245</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 25KW FREQUENCIA 15-30KHZ 380V - MARCA JAMO SERIE E05911
@@ -6329,93 +6437,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>2024-04-29</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R53" t="n">
+      <c r="R54" t="n">
         <v>4280</v>
       </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="n">
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="n">
         <v>4280</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>4280.00000000</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
+    <row r="55">
+      <c r="A55" s="1" t="n">
         <v>45399</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>5105</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>9191</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>618 - PROSPAR INDUSTRIA E COMERCIO DE PARAFUSOS LTDA - EPP</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>618 - PROSPAR - IND COM PARAFUSOS LTDA</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA AUTOMATICA
@@ -6447,105 +6555,105 @@
 QTD.: 2,000 MT</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
         <is>
           <t>4134-1</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R54" t="n">
+      <c r="R55" t="n">
         <v>3080</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>1580.06000000</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="n">
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="n">
         <v>4660.06</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>4660.06000000</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
+    <row r="56">
+      <c r="A56" s="1" t="n">
         <v>45377</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>4979</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>8944</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>3025 - COPECAR INDUSTRIA E COMERCIO DE PECAS AGRICOLAS LTDA</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>3025 - COPECAR IND E COM PECAS AGRICOLAS LT</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 TEMPERA DOIS EIXOS 160KW
@@ -6577,105 +6685,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
         <is>
           <t>4243-1</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R55" t="n">
+      <c r="R56" t="n">
         <v>9120</v>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>4332.38000000</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="n">
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="n">
         <v>13452.38</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>13452.39000000</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
+    <row r="57">
+      <c r="A57" s="1" t="n">
         <v>45364</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>4922</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>8894</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>COMPRA DE PRODUTO</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 ORCAMENTO PECAS DE REPOSICAO PARA MAQUINA TRATAMENTO TERMICO 017 NUMERO DE SERIE 10680-52
@@ -6690,93 +6798,93 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>2024-03-28</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R56" t="n">
+      <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>11673.72000000</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="n">
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="n">
         <v>11673.72</v>
       </c>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr">
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
         <is>
           <t>11673.72000000</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
+    <row r="58">
+      <c r="A58" s="1" t="n">
         <v>45371</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>4958</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>8965</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MAQUINA DE TEMPERA
@@ -6797,93 +6905,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>2024-03-23</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R57" t="n">
+      <c r="R58" t="n">
         <v>3107</v>
       </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="n">
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="n">
         <v>3107</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>3107.00000000</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
+    <row r="59">
+      <c r="A59" s="1" t="n">
         <v>45370</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>4951</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>8787</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA - ME</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA MANUEL 3 UNIDADES
@@ -6904,93 +7012,93 @@
 QTD.: 1.000,000 KM</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>2024-03-22</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R58" t="n">
+      <c r="R59" t="n">
         <v>8028</v>
       </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="n">
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="n">
         <v>8028</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>8028.00000000</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
+    <row r="60">
+      <c r="A60" s="1" t="n">
         <v>45359</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>4906</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>8812</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>193 - FORJAFIX ELEMENTOS DE FIXACAO LTDA</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>193 - FORJAFIX ELEMENTOS DE FIXACAO LTDA</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO INDUCAO ALIMENTACAO AUTOMATICA - 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -7020,105 +7128,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>2024-03-11</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
         <is>
           <t>4218-1</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R59" t="n">
+      <c r="R60" t="n">
         <v>4968.5</v>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>5942.14000000</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="n">
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="n">
         <v>10910.64</v>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>10910.65000000</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
+    <row r="61">
+      <c r="A61" s="1" t="n">
         <v>45345</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>4839</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>5206</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO MANUAL 40KW - 380V - FABRICACAO 3MI
@@ -7135,93 +7243,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>2024-02-25</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R60" t="n">
+      <c r="R61" t="n">
         <v>4890</v>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="n">
         <v>4890</v>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>4890.00000000</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
+    <row r="62">
+      <c r="A62" s="1" t="n">
         <v>45324</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>4758</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>6231</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA FORJA - POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -7247,105 +7355,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
         <is>
           <t>3841-1</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R61" t="n">
+      <c r="R62" t="n">
         <v>7787.2</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>1759.00000000</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="n">
         <v>9546.200000000001</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>9603.37000000</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
+    <row r="63">
+      <c r="A63" s="1" t="n">
         <v>45301</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>4658</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>8443</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>198 - METALTORK INDUSTRIA E COMERCIO DE AUTO PECAS LIMITADA</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>198 - METALTORK INDUSTRIA E COMERCIO DE AUTO PECAS LIMITADA</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO FORJA ALIMENTACAO AUTOMATICA - 120KW FREQUENCIA 15-30KHZ 380V - MARCA 3MI
@@ -7363,105 +7471,105 @@
 QTD.: 2,000 PC</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
         <is>
           <t>3745-1</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R62" t="n">
+      <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>7500.00000000</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="n">
         <v>7500</v>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>7500.00000000</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
+    <row r="64">
+      <c r="A64" s="1" t="n">
         <v>45181</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>4270</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>8109</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM UM EQUIPAMENTO MARCA JAMO AQUECIMENTO CONTINUO DE FIO MAQUINA
@@ -7485,93 +7593,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R63" t="n">
+      <c r="R64" t="n">
         <v>6563.6</v>
       </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="n">
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="n">
         <v>6563.6</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>6563.60000000</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
+    <row r="65">
+      <c r="A65" s="1" t="n">
         <v>45034</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>3756</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>7390</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>1444 - ALLENFIX COMERCIO DE PARAFUSOS E FIXACOES LTDA</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>1444 - ALLENFIX COMERCIO DE PARAFUSOS E FIXACOES LTDA</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM DOIS EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO MARCA 3MI
@@ -7585,93 +7693,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R64" t="n">
+      <c r="R65" t="n">
         <v>8590</v>
       </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="n">
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="n">
         <v>8590</v>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>8590.00000000</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
+    <row r="66">
+      <c r="A66" s="1" t="n">
         <v>45034</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>3755</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>7401</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 SUBSTITUIR O FRONTAL GERAL DO TRANSFORMADOR MAQUINA 100KW -15-30KHZ FORJA MARCA 3MI POIS O MESMO ESTA BASTANTE AVARIADO
@@ -7688,105 +7796,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
         <is>
           <t>3495-1</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R65" t="n">
+      <c r="R66" t="n">
         <v>720</v>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>1961.75000000</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="n">
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="n">
         <v>2681.75</v>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>2681.75000000</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
+    <row r="67">
+      <c r="A67" s="1" t="n">
         <v>44837</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>3226</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>6694</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>598 - METALPRIME USINAGEM / ORION</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>598 - METALPRIME USINAGEM SERIADA EIRELI</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO TRATAMENTO TERMICO 
@@ -7803,93 +7911,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R66" t="n">
+      <c r="R67" t="n">
         <v>7540</v>
       </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="n">
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="n">
         <v>7540</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>7540.00000000</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
+    <row r="68">
+      <c r="A68" s="1" t="n">
         <v>44837</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>3228</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>6539</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 25KW FREQUENCIA 15-30KHZ 380V - MARCA JAMO SERIE E05911
@@ -7904,93 +8012,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>2022-10-05</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R67" t="n">
+      <c r="R68" t="n">
         <v>3911</v>
       </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="n">
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="n">
         <v>3911</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>3911.00000000</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
+    <row r="69">
+      <c r="A69" s="1" t="n">
         <v>44750</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>2992</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>6403</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE FORJA 100KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -8021,105 +8129,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
         <is>
           <t>2609-1</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R68" t="n">
+      <c r="R69" t="n">
         <v>1350.2</v>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>8366.86000000</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="n">
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="n">
         <v>9717.059999999999</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>9717.06000000</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
+    <row r="70">
+      <c r="A70" s="1" t="n">
         <v>44722</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>2904</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>5745</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI ME</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO TEMPERA POR INDUCAO - 60KW FREQUENCIA 15-30KHZ 380V - MARCA 3MI
@@ -8135,93 +8243,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>2022-06-17</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R69" t="n">
+      <c r="R70" t="n">
         <v>5200</v>
       </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="n">
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="n">
         <v>5200</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>5200.00000000</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
+    <row r="71">
+      <c r="A71" s="1" t="n">
         <v>44719</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>2887</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>6299</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>2846 - MHT INDUSTRIA E COMERCIO DE COMPONENTES AUTOMOTIVOS LTDA</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>2846 - MHT INDUSTRIA E COMERCIO DE COMPONENTES AUTOMOTIVOS LTDA</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO FORJA ALIMENTACAO PNEUMATICO COM CALHA 120KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -8235,93 +8343,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R70" t="n">
+      <c r="R71" t="n">
         <v>4890</v>
       </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="n">
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="n">
         <v>4890</v>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>4890.00000000</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
+    <row r="72">
+      <c r="A72" s="1" t="n">
         <v>44720</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>2893</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>6328</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO MANUAL FORJA 120KW FREQUENCIA 15-30KHZ - 380V
@@ -8354,105 +8462,105 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>2022-06-09</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
         <is>
           <t>2579-1</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R71" t="n">
+      <c r="R72" t="n">
         <v>2836.6</v>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>2218.84000000</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="n">
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="n">
         <v>5055.44</v>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>5055.46000000</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
+    <row r="73">
+      <c r="A73" s="1" t="n">
         <v>44708</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>2847</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>6274</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO MANUAL FORJA 120KW FREQUENCIA 15-30KHZ - 380V
@@ -8485,105 +8593,105 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>2022-05-28</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
         <is>
           <t>2563-1</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R72" t="n">
+      <c r="R73" t="n">
         <v>2639.2</v>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>1633.42000000</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="n">
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="n">
         <v>4272.62</v>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>4272.63000000</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
+    <row r="74">
+      <c r="A74" s="1" t="n">
         <v>44691</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>6204</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA AQUECIMENTO INDUTIVO MANUAL - 100KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -8615,105 +8723,105 @@
 QTD.: 3,000 M</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>2022-05-12</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
         <is>
           <t>2548-1</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R73" t="n">
+      <c r="R74" t="n">
         <v>3780.8</v>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>2757.50000000</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="n">
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="n">
         <v>6538.3</v>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="V74" t="inlineStr">
         <is>
           <t>6538.31000000</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
+    <row r="75">
+      <c r="A75" s="1" t="n">
         <v>44662</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>2714</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>5965</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO PNEUMATICO - 40KW 380V FREQUENCIA 15-30KHZ
@@ -8724,93 +8832,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>2022-04-16</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R74" t="n">
+      <c r="R75" t="n">
         <v>4230</v>
       </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="n">
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="n">
         <v>4230</v>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>4230.00000000</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
+    <row r="76">
+      <c r="A76" s="1" t="n">
         <v>44645</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>2666</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>6078</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO EM DOIS EQUIPAMENTO FORJARIA 10 E 40KW
@@ -8831,105 +8939,105 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>2022-03-26</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
         <is>
           <t>2499-1</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R75" t="n">
+      <c r="R76" t="n">
         <v>838.8</v>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>2164.23000000</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="n">
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="n">
         <v>3003.03</v>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>3003.03000000</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
+    <row r="77">
+      <c r="A77" s="1" t="n">
         <v>44397</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>5194</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>1425 - ZL BRASIL</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>1425 - ZUCOLLO AUTO PARTS IND COM EXP IMP LTDA</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TEMPERA POR INDUCAO AQUECIMENTO DUPLO - 160KW - 380V FABRICACAO 3MI
@@ -8944,89 +9052,89 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>2021-07-23</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R76" t="n">
+      <c r="R77" t="n">
         <v>4820</v>
       </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="n">
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="n">
         <v>4820</v>
       </c>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr">
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
         <is>
           <t>4820.00000000</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
+    <row r="78">
+      <c r="A78" s="1" t="n">
         <v>44397</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>1944</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>5349</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FABRICACAO 3MI ALIMENTACAO MANUAL - 100KW - 380V - FREQUENCIA DE TRABALHO 15-30KHZ
@@ -9038,93 +9146,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>2021-07-22</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R77" t="n">
+      <c r="R78" t="n">
         <v>3800</v>
       </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="n">
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="n">
         <v>3800</v>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="V78" t="inlineStr">
         <is>
           <t>3800.00000000</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="W78" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
+    <row r="79">
+      <c r="A79" s="1" t="n">
         <v>44368</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>1887</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>5301</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE FORJARIA ALIMENTACAO PNEUMATICA E CALHA 120KW
@@ -9140,93 +9248,93 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>2021-06-23</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R78" t="n">
+      <c r="R79" t="n">
         <v>4600</v>
       </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="n">
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="n">
         <v>4600</v>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="V79" t="inlineStr">
         <is>
           <t>4600.00000000</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="W79" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
+    <row r="80">
+      <c r="A80" s="1" t="n">
         <v>44334</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>1793</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>5193</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO DUPLO 160KW DE FABRICACAO 3MI
@@ -9242,89 +9350,89 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>2021-05-21</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R79" t="n">
+      <c r="R80" t="n">
         <v>4600</v>
       </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="n">
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="n">
         <v>4600</v>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>4600.00000000</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="W80" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
+    <row r="81">
+      <c r="A81" s="1" t="n">
         <v>44903</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>3397</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>4556 - INNIO JEANBACKER MOTORES A GAS LTDA.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>4556 - JEANBACKER MOTORES A GAS LTDA.</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>FABRICACAO DE EQUIPAMENTO NOVO</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>FORNECER 01 AQUECEDOR PARA SACAR SEDE DE VALVULAS 
 25KW - FREQUENCIA 15-30KHZ - 380V
@@ -9339,41 +9447,41 @@
 -GARANTIA EXTENDIDA 24 MESES, ONDE APÓS O START DO EQUIPAMENTO A CADA 6 MESES DEVEREMOS FAZER UMA MANUTENÇÃO PREVENTIVA NO CLIENTE.</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
         <is>
           <t>Produzido: 11651 (10895-14)</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>3412-1</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="n">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>117000.00000000</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="n">
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="n">
         <v>117000</v>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>117000.00000000</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="W81" t="inlineStr">
         <is>
           <t>0.00000000</t>
         </is>

--- a/Pedidos_Manutencao.xlsx
+++ b/Pedidos_Manutencao.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>EM EXECUCAO</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -623,27 +623,39 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>7289-1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>3210</v>
+        <v>3049.5</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>588.53000000</t>
+          <t>559.10000000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>3798.53</v>
+        <v>3608.6</v>
       </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3608.60000000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">

--- a/Pedidos_Manutencao.xlsx
+++ b/Pedidos_Manutencao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W83"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,72 +526,173 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Recebido</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>AReceber</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3MI INDUCAO - SC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8601</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12.563.613/0002-05</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>14327</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1764 - INDUCHAMA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SP - MANUTENÇÃO PREVENTIVA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1764 - INDUCHAMA TRATAMENTO TERMICO EIRELI EPP</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTO:
+MANUTENÇÃO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO POR INDUÇÃO 160KW TENSAO 380V FREQUENCIA 15-27KHZ
+DEFEITO:
+NESSA MANUTENÇÃO PREVENTIVA SÃO VERIFICADOS, LIMPOS E AJUSTADOS TODOS OS ITENS MENCIONADOS EM NOSSO CHECK LIST ANEXO.
+FOI VERIFICADO A NECESSIDADE DA SUBSTITUIÇÃO DA PLACA PRINCIPAL DO CONJUNTO (ESSA PEÇA FOI FORNECIDA PELA 3MI) E UM CAPACITOR DO LINK (ESSA PEÇA FOI FORNECIDA PELO CLIENTE)
+LAUDO/OBS.:
+SERVIÇO REALIZADO EM 29/9
+O EQUIPAMENTO FOI ACOMPANHADO TRABALHANDO POR ALGUMAS HORAS O QUAL NÃO APRESENTOU NENHUM PROBLEMA E ESTGÁ EM FUNCIONAMENTO.
+COR: 
+SERVICOS:
+6503 - DESLOCAMENTO
+QTD.: 228,000 KM
+6505 - PEDAGIOS
+QTD.: 1,000 UN
+1341 - SERVICOS PRESTADOS DIVERSOS
+QTD.: 1,000 UN
+PRODUTOS:
+6425 - PLACA DE CONTROLE GERADOR 3MI
+QTD.: 1,000 UN</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>7340-1</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>SERGIO PRATES PEREIRA</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>3258.92</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4461.43000000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>7720.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>46295</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>8592</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>14159</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>3913 - FITA CABO - CARGA TEXTIL</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SP - MANUTENÇÃO PREVENTIVA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>3913 - CARGA TEXTIL IND.E COM.DE EQUIP.DE MOV.MODAL LTDA.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>EM EXECUCAO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA AUTOMATICA OU MANUAL POTENCIA 10, 25 OU 40KW
@@ -611,89 +712,95 @@
 QTD.: 4,000 UN</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>7343-1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="R3" t="n">
         <v>3320</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>817.74000000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
         <v>4137.74</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>46287</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>8564</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>14266</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1619 - JS BRONZINA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SP - MANUTENÇÃO PREVENTIVA</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>1619 - JS INDUSTRIA DE BRONZINA LTDA</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>EM EXECUCAO</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO AQUECIMENTO DE TUDOS POTENCIA 80, 100 E 120KW - TROCADOR DE CALOR
@@ -710,89 +817,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>4560</v>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>4560</v>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>4560.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    <row r="5">
+      <c r="A5" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>8549</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>14242</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2643 - SRC MOLAS INDUSTRIAIS</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>SP - MANUTENÇÃO PREVENTIVA</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2643 - INDUSTRIA E COMERCIO DE MOLAS SRC LTDA.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO FORJA MANUAL 25 E 60KW - TROCADOR DE CALOR
@@ -818,101 +919,95 @@
 QTD.: 6,000 M</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>7289-1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>3049.5</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>559.10000000</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="n">
         <v>3608.6</v>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>3608.60000000</t>
-        </is>
-      </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    <row r="6">
+      <c r="A6" s="1" t="n">
         <v>46267</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>8496</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>13782</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 120KW - 380V FREQUENCIA 15-30KHZ
@@ -930,89 +1025,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>5932</v>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
         <v>5932</v>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>5932.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    <row r="7">
+      <c r="A7" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>8466</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>9631</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>1703 - FORJARIA E SERRALHERIA MOREIRA LTDA. ME</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>1703 - FORJARIA E SERRALHERIA MOREIRA LTDA. ME</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO POR INDUCAO MANUAL 25KW - 380V FREQUENCIA 15-30KHZ FABRICACAO/MARCA: 3MI
@@ -1030,89 +1119,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>4980</v>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="n">
         <v>4980</v>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>4980.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    <row r="8">
+      <c r="A8" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>7904</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>13086</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4111 - MOTOPPAR</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>4111 - MOTOPPAR IND COM DE AUTOMATIZADORES LTDA</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENÇÃO PREVENTIVA EM EQUIPAMENTOS DE TEMPERA POR INDUÇÃO 40KW TENSA0 380V FREQUENCIA 15-27KHZ
@@ -1136,93 +1219,83 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>10319.04</v>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="n">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="n">
         <v>10319.04</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>10319.04000000</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    <row r="9">
+      <c r="A9" s="1" t="n">
         <v>46073</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>7836</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>12727.1</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE AQUECIMENTO POR INDUÇÃO 40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -1244,93 +1317,83 @@
 QTD.:</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>9790</v>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="n">
         <v>9790</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>9790.00000000</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+    <row r="10">
+      <c r="A10" s="1" t="n">
         <v>46035</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>7699</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>12622</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENÇÃO REALIZADA EQUIPAMENTO FORJARIA 160KW TENSAO 380V FREQUENCIA 15-26KHZ
@@ -1361,105 +1424,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>6428-1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>2427.32</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>746.50000000</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="n">
         <v>3173.82</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>3173.82000000</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    <row r="11">
+      <c r="A11" s="1" t="n">
         <v>46001</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>7639</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>6215</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>736 - METALFLEXO</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>736 - METALFLEXO IND.COM.FER.FLEXOGRAFIA LTDA</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA TEMPERA - POTENCIA 40KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -1473,93 +1526,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2025-12-17</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>5395.2</v>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="n">
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="n">
         <v>5395.2</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>5395.20000000</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>7605</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>12222</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO PNEUMATICO - 40KW 380V FREQUENCIA 15-30KHZ
@@ -1576,93 +1619,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-01-08</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>4836</v>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="n">
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="n">
         <v>4836</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>4836.00000000</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    <row r="13">
+      <c r="A13" s="1" t="n">
         <v>45979</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>7554</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>11947</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>7069 - ZANINI RENK</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>7069 - ZANINI RENK EQUIPAMENTOS INDUSTRIAIS LTDA</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE AQUECIMENTO POR INDUÇÃO PARA MONTAGENS DE ROLAMENTOS POR DILATAÇÃO TERMICO MARCA JAMO
@@ -1688,105 +1721,95 @@
 QTD.: 1,000 UNID</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>5688-1</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>1939.42</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>3262.00000000</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="n">
         <v>5201.42</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>5201.42000000</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    <row r="14">
+      <c r="A14" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>7374</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>12053</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI/JAMO - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -1808,93 +1831,83 @@
 QTD.: 3,000 UN</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R14" t="n">
         <v>12600</v>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="n">
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="n">
         <v>12600</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>12600.00000000</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    <row r="15">
+      <c r="A15" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>7373</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>12230</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI/JAMO - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -1916,93 +1929,83 @@
 QTD.: 3,000 UN</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>8400</v>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="n">
         <v>8400</v>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>8400.00000000</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    <row r="16">
+      <c r="A16" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>7270</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>12067</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 PEÇAS PARA SER SUBSTITUIDA EM MANUTENÇÃO PREVENTIVA DE EQUIPAMENTO
@@ -2015,105 +2018,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>6038-1</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>4460.40000000</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="n">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
         <v>4460.4</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>4460.40000000</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    <row r="17">
+      <c r="A17" s="1" t="n">
         <v>45909</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>7254</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>12054</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI/JAMO - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -2134,93 +2127,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>5690</v>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="n">
         <v>5690</v>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>5690.00000000</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    <row r="18">
+      <c r="A18" s="1" t="n">
         <v>45896</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>7202</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>11935</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM UM EQUIPAMENTO MARCA JAMO AQUECIMENTO CONTINUO DE FIO MAQUINA
@@ -2250,89 +2233,87 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>5339.6</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>4460.40000000</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
         <v>9800</v>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="n">
         <v>45859</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>7055</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>11783</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2472 - FIXABEM SERVICOS DE FERRAGENS E FERRAMENTAS LTDA.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>2472 - FIXA BEM SERVICOS DE FERRAGENS E FERRAMENTAS LTDA</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENÇÃO PREVENTIVA EM EQUIPAMENTOS DE FORJA MANUAL MARCA JAMO - 80 KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -2348,93 +2329,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>6140</v>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="n">
         <v>6140</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>6140.00000000</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    <row r="20">
+      <c r="A20" s="1" t="n">
         <v>45839</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>6959</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>11663</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA MANUAL 60KW TENSAO 380V FREQUENCIA 15-30KHZ MARCA JAMO
@@ -2447,105 +2418,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>5732-1</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>3603.42000000</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="n">
         <v>3603.42</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>3603.43000000</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    <row r="21">
+      <c r="A21" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>6918</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>11649</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 CONFORME SOLICITADO PELO SR. MANOEL EM JÁ PRÉ AGENDADO PARA EXECUTARMOS EM 01/07/2025, MANUTENÇÃO PREVENTIVA NO EQUIPAMENTO FORJA MANUAL 60KW NUMERO DE SERIE E-03788
@@ -2581,97 +2542,87 @@
 QTD.: 22,000 UN</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2025-06-28</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>2610.26</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>2662.56000000</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="n">
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="n">
         <v>5272.82</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>5272.82000000</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+    <row r="22">
+      <c r="A22" s="1" t="n">
         <v>45833</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>6908</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>11625</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 25KW FREQUENCIA 15-30KHZ 380V - MARCA JAMO SERIE E05911
@@ -2687,93 +2638,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R22" t="n">
         <v>4390</v>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="n">
         <v>4390</v>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>4390.00000000</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
+    <row r="23">
+      <c r="A23" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>6841</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>11481</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 CONFORME SOLICITADO PELO SR. MANOEL PRODUÇÃO BRASIMPAR REALIZAMOS UMA MANUTENÇÃO PREVENTIVA NO EQUIPAMENTO FORJA MANUAL 40KW NUMERO DE SERIE E-03381/5
@@ -2810,105 +2751,95 @@
 QTD.: 1,500 M</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
         <is>
           <t>5642-1</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>2222.06</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>2059.31000000</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="n">
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="n">
         <v>4281.37</v>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>4281.38000000</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
+    <row r="24">
+      <c r="A24" s="1" t="n">
         <v>45812</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>6833</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>11286</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>4859 - LORD FERRAMENTAS</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>4859 - LORD EZEQUIEL INDUSTRIA E COMERCIO DE FERRAMENTAS LTDA</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO POR INDUÇÃO 40KW TENSÃO 380V FREQUENCIA 15-27KHZ
@@ -2927,93 +2858,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>4600</v>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="n">
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="n">
         <v>4600</v>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>4600.00000000</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
+    <row r="25">
+      <c r="A25" s="1" t="n">
         <v>45754</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>6648</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>11219</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA AUTOMATICA - 3MI - 100KW TENSAO 380V FREQUENCIA 15-30 KHZ
@@ -3061,105 +2982,95 @@
 QTD.: 3,000 PC</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>2025-04-08</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
         <is>
           <t>5425-1</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>2425.6</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>7562.19000000</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="n">
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="n">
         <v>9987.790000000001</v>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>9987.79000000</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
+    <row r="26">
+      <c r="A26" s="1" t="n">
         <v>45744</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>6621</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>11181</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA - ME</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>DEFEITO:
 MANUTENCAO PREVENTIVA DE 4 MAQUINAS E 1 MAQUINA DE TEMPERA
@@ -3178,93 +3089,83 @@
 QTD.: 4,000 UN</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>8400</v>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="n">
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="n">
         <v>8400</v>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>8400.00000000</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
+    <row r="27">
+      <c r="A27" s="1" t="n">
         <v>45699</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>6456</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>10919</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE AQUECIMENTO POR INDUÇÃO 40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -3284,93 +3185,83 @@
 QTD.: 7,000 HR</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>2025-02-16</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>10100</v>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="n">
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="n">
         <v>10100</v>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>10100.00000000</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
+    <row r="28">
+      <c r="A28" s="1" t="n">
         <v>45695</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>6446</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>10907</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA NOS 3 EQUIPAMENTOS DE TEMPERA 3MI 
@@ -3393,93 +3284,83 @@
 QTD.: 16,000 HR</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>2025-02-12</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>6845</v>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="n">
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="n">
         <v>6845</v>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>6845.00000000</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
+    <row r="29">
+      <c r="A29" s="1" t="n">
         <v>45680</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>6402</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>10816</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA FORJA - POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -3499,93 +3380,83 @@
 QTD.: 3,000 UN</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>2025-01-26</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>7787.2</v>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="n">
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="n">
         <v>7787.2</v>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>7787.20000000</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
+    <row r="30">
+      <c r="A30" s="1" t="n">
         <v>45677</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>6382</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>7457</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2612 - DYNAR AUTOMATIZACAO INDUSTRIAL LTDA</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>2612 - DYNAR AUTOMATIZACAO INDUSTRIAL LTDA</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS SOLDA POR BRASAGEM - 10KW - TENSAO 380V
@@ -3603,93 +3474,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>2025-01-23</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>3680</v>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="n">
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="n">
         <v>3680</v>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>3680.00000000</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
+    <row r="31">
+      <c r="A31" s="1" t="n">
         <v>45644</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>6284</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>10559</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>203 - USINA DA PECA</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>203 - USINA DA PECA IND E COMERCIO DE PECAS E MAQ. AGRIC. LTDA</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TRATAMENTO TERMICO DUPLO 160KW TENSAO 380V - FREQUENCIA 15-30KHZ
@@ -3728,105 +3589,95 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>2024-12-21</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
         <is>
           <t>5112-1</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>7274.87</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>8225.12000000</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="n">
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="n">
         <v>15499.99</v>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>15500.00000000</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
+    <row r="32">
+      <c r="A32" s="1" t="n">
         <v>45609</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>6146</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>10546</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA JAMO - POTENCIA 100KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -3841,89 +3692,79 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>2024-11-14</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>4200</v>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="n">
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="n">
         <v>4200</v>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>4200.00000000</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
+    <row r="33">
+      <c r="A33" s="1" t="n">
         <v>45604</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>6118</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU SEM - MARCA 3MI - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -3944,93 +3785,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>4200</v>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="n">
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="n">
         <v>4200</v>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>4200.00000000</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
+    <row r="34">
+      <c r="A34" s="1" t="n">
         <v>45595</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>6077</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>9789</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA COM ALIMENTACAO PNEUMATICA - 25/40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4052,105 +3883,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
         <is>
           <t>5004-1</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>831.2</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>667.61000000</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="n">
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="n">
         <v>1498.81</v>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1498.82000000</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
+    <row r="35">
+      <c r="A35" s="1" t="n">
         <v>45588</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>6030</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>10419</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU8 SEM - MARCA 3MI - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4175,93 +3996,83 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>2024-10-24</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>8400</v>
       </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="n">
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="n">
         <v>8400</v>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>8400.00000000</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
+    <row r="36">
+      <c r="A36" s="1" t="n">
         <v>45583</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>6015</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>10342</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>981 - INDUSTRIAS GERAIS DE PARAFUSOS INGEPAL LTDA</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>981 - INDS.GERAIS DE PARAFUSOS INGEPAL LTDA</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO PNEUMATICO - 40KW / 100KW 380V FREQUENCIA 15-30KHZ
@@ -4278,93 +4089,83 @@
 VERIFICAR COM O CLIENTE SE JÁ QUER DEIXAR AGENDADO DATA PARA PROXIMA MAQUINA</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>4450</v>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="n">
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="n">
         <v>4450</v>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>4450.00000000</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
+    <row r="37">
+      <c r="A37" s="1" t="n">
         <v>45575</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>5968</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>10305</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>1469 - MRS - IRMA CESTARI</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>1469 - IND. E COM. DE PECAS MRS LTDA</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE TEMPERA POR INDUCAO DUPLO (HORIZONTAL E VERTICAL) 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4382,105 +4183,95 @@
 QTD.: 2,000 PC</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
         <is>
           <t>4889-1</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>9540.30000000</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="n">
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="n">
         <v>9540.299999999999</v>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>9540.30000000</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
+    <row r="38">
+      <c r="A38" s="1" t="n">
         <v>45568</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>5928</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>10174</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS E MANUAIS COM CALHA OU8 SEM - MARCA 3MI - POTENCIA 40, 100 E 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4505,93 +4296,83 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>8400</v>
       </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="n">
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
         <v>8400</v>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>8400.00000000</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
+    <row r="39">
+      <c r="A39" s="1" t="n">
         <v>45568</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>5927</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>10172</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>3913 - FITA CABO - CARGA TEXTIL</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>3913 - CARGA TEXTIL IND.E COM.DE EQUIP.DE MOV.MODAL LTDA.</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO AUTOMATICOS COM CALHA MARCA 3MI - POTENCIA 40KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -4608,93 +4389,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>4452</v>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="n">
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="n">
         <v>4452</v>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>4452.00000000</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
+    <row r="40">
+      <c r="A40" s="1" t="n">
         <v>45546</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>5808</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>9193</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>4049 - GAR AUTO PARTS</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>4049 - GAR IND. COM. DE PECAS AUTOMOTIVAS LTDA.</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA JAMO POTENCIA 100KW
@@ -4718,105 +4489,95 @@
 QTD.: 600,000 KM</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
         <is>
           <t>4809-1</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R39" t="n">
+      <c r="R40" t="n">
         <v>3740</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>1688.65000000</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="n">
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="n">
         <v>5428.65</v>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>5428.65000000</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
+    <row r="41">
+      <c r="A41" s="1" t="n">
         <v>45546</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>5805</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>10113</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MAQUINAS DE TEMPERA
@@ -4839,93 +4600,83 @@
 QTD.: 16,000 HR</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>7505</v>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="n">
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="n">
         <v>7505</v>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>7505.00000000</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
+    <row r="42">
+      <c r="A42" s="1" t="n">
         <v>45545</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>5804</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>10124</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI ME</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TEMPERA 60KW - TENSAO 380V
@@ -4941,105 +4692,95 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
         <is>
           <t>4786-1</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R41" t="n">
+      <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>2168.25000000</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="n">
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="n">
         <v>2168.25</v>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2168.26000000</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
+    <row r="43">
+      <c r="A43" s="1" t="n">
         <v>45538</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>5756</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>9854</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO TEMPERA POR INDUCAO CONTRA PONTA DUPLO POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -5061,93 +4802,83 @@
 AGENDADO PARA 05 E 06/09/24.</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R42" t="n">
+      <c r="R43" t="n">
         <v>9675.459999999999</v>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="n">
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="n">
         <v>9675.459999999999</v>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>9675.46000000</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
+    <row r="44">
+      <c r="A44" s="1" t="n">
         <v>45531</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>5714</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>9996</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TRATAMENTO TERMICO TEMPERA POR INDUCAO ENTRE PONTAS DUPLO - 160KW - 380V FREQUENCIA 15-30KHZ
@@ -5177,105 +4908,95 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>2024-08-29</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
         <is>
           <t>4731-1</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R43" t="n">
+      <c r="R44" t="n">
         <v>1543.6</v>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>6456.39000000</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="n">
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="n">
         <v>7999.99</v>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>8000.00000000</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
+    <row r="45">
+      <c r="A45" s="1" t="n">
         <v>45527</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>5698</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>8655</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>1469 - MRS - IRMA CESTARI</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>1469 - IND. E COM. DE PECAS MRS LTDA</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE TEMPERA POR INDUCAO DUPLO POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -5293,93 +5014,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>2024-08-26</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R45" t="n">
         <v>7879.2</v>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="n">
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="n">
         <v>7879.2</v>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>7879.20000000</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
+    <row r="46">
+      <c r="A46" s="1" t="n">
         <v>45496</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>5554</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>9733</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>1390 - INOX PAR INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>1390 - INOX PAR INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO POR INDUCAO FORJA MANUAL 3MI - POTENCIA 25KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -5402,105 +5113,95 @@
 QTD.: 1,000 UND</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
         <is>
           <t>4649-1</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R45" t="n">
+      <c r="R46" t="n">
         <v>5270</v>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>4429.43000000</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="n">
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="n">
         <v>9699.43</v>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>9699.43000000</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
+    <row r="47">
+      <c r="A47" s="1" t="n">
         <v>45491</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>5528</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>9806</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EQUIPAMENTO 60KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -5518,93 +5219,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>2024-07-19</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R47" t="n">
         <v>4120</v>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="n">
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="n">
         <v>4120</v>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>4120.00000000</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
+    <row r="48">
+      <c r="A48" s="1" t="n">
         <v>45488</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>5507</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>9760</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>618 - PROSPAR INDUSTRIA E COMERCIO DE PARAFUSOS LTDA - EPP</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>618 - PROSPAR - IND COM PARAFUSOS LTDA</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA AUTOMATICA
@@ -5629,105 +5320,95 @@
 QTD.: 7,000 M</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
         <is>
           <t>4583-1</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R48" t="n">
         <v>3080</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>1045.47000000</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="n">
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="n">
         <v>4125.47</v>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>4125.47000000</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
+    <row r="49">
+      <c r="A49" s="1" t="n">
         <v>45479</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>5468</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI ME</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIOPAMENTO TRATAMENTO TERMICO DUPLO EIXO - 60KW
@@ -5744,93 +5425,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R48" t="n">
+      <c r="R49" t="n">
         <v>5300</v>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="n">
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="n">
         <v>5300</v>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>5300.00000000</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
+    <row r="50">
+      <c r="A50" s="1" t="n">
         <v>45455</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>5367</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>9588</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>752 - PERFIL FACAS</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>752 - PERFIL INDUSTRIA DE FACAS ROTATIVAS LTDA - EPP</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA TEMPERA - POTENCIA 40KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -5844,93 +5515,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>2024-06-15</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R49" t="n">
+      <c r="R50" t="n">
         <v>5000</v>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="n">
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="n">
         <v>5000</v>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>5000.00000000</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
+    <row r="51">
+      <c r="A51" s="1" t="n">
         <v>45450</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>5343</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>9536</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO ALIMENTACAO MANUAL 
@@ -5948,93 +5609,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R50" t="n">
+      <c r="R51" t="n">
         <v>4120</v>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="n">
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="n">
         <v>4120</v>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>4120.00000000</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
+    <row r="52">
+      <c r="A52" s="1" t="n">
         <v>45441</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>5311</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>9516</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA MAQUINA 40KW - TENSAO 380V - FREQUENCIA 15-30KHZ
@@ -6044,93 +5695,83 @@
 QTD.: 3.600,000 UN</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>2024-05-30</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="R52" t="n">
         <v>3600</v>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="n">
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="n">
         <v>3600</v>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>3600.00000000</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
+    <row r="53">
+      <c r="A53" s="1" t="n">
         <v>45432</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>5246</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>9183</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>568 - TECSTAM FORJARIA E ESTAMPARIA LTDA - EPP</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>568 - TEC-STAM FORJARIA E ESTAMPARIA LTDA</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA AUTOMATICA 
@@ -6162,105 +5803,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>2024-05-23</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
         <is>
           <t>4410-1</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R52" t="n">
+      <c r="R53" t="n">
         <v>1733.6</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>3736.95000000</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="n">
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="n">
         <v>5470.55</v>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>5470.55000000</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
+    <row r="54">
+      <c r="A54" s="1" t="n">
         <v>45429</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>5244</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>9362</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>2968 - VAZ VAZ METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>2968 - VAZ E VAZ METALURGICA LTDA ME</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>DEFEITO:
 EQUIPAMENTO COM FALHA DE ALTA CORRENTE
@@ -6285,105 +5916,95 @@
 QTD.: 6,000 PC</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
         <is>
           <t>4406-1</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R53" t="n">
+      <c r="R54" t="n">
         <v>4519.71</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>2874.48000000</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="n">
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="n">
         <v>7394.19</v>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>7394.20000000</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
+    <row r="55">
+      <c r="A55" s="1" t="n">
         <v>45412</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>5169</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>9297.1</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTOS DE TEMPRAS
@@ -6416,105 +6037,95 @@
 QTD.: 16,000 M</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>2024-05-20</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
         <is>
           <t>4454-1</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R54" t="n">
+      <c r="R55" t="n">
         <v>11405</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>4749.67000000</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="n">
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="n">
         <v>16154.67</v>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>16154.68000000</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
+    <row r="56">
+      <c r="A56" s="1" t="n">
         <v>45412</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>5168</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>9271</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA AUTOMATICA M160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -6537,105 +6148,95 @@
 QTD.: 2,000 PC</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>2024-05-03</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
         <is>
           <t>4348-1</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R55" t="n">
+      <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>7791.25000000</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="n">
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="n">
         <v>7791.25</v>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>7791.25000000</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
+    <row r="57">
+      <c r="A57" s="1" t="n">
         <v>45404</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>5130</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>9245</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 25KW FREQUENCIA 15-30KHZ 380V - MARCA JAMO SERIE E05911
@@ -6650,93 +6251,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>2024-04-29</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R56" t="n">
+      <c r="R57" t="n">
         <v>4280</v>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="n">
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="n">
         <v>4280</v>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>4280.00000000</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
+    <row r="58">
+      <c r="A58" s="1" t="n">
         <v>45399</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>5105</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>9191</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>618 - PROSPAR INDUSTRIA E COMERCIO DE PARAFUSOS LTDA - EPP</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>618 - PROSPAR - IND COM PARAFUSOS LTDA</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA AUTOMATICA
@@ -6768,105 +6359,95 @@
 QTD.: 2,000 MT</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>2024-04-20</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
         <is>
           <t>4134-1</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R57" t="n">
+      <c r="R58" t="n">
         <v>3080</v>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>1580.06000000</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="n">
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="n">
         <v>4660.06</v>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>4660.06000000</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
+    <row r="59">
+      <c r="A59" s="1" t="n">
         <v>45377</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>4979</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>8944</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>3025 - COPECAR INDUSTRIA E COMERCIO DE PECAS AGRICOLAS LTDA</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>3025 - COPECAR IND E COM PECAS AGRICOLAS LT</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 TEMPERA DOIS EIXOS 160KW
@@ -6898,105 +6479,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>2024-03-29</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
         <is>
           <t>4243-1</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R58" t="n">
+      <c r="R59" t="n">
         <v>9120</v>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>4332.38000000</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="n">
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="n">
         <v>13452.38</v>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>13452.39000000</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
+    <row r="60">
+      <c r="A60" s="1" t="n">
         <v>45371</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>4958</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>8965</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MAQUINA DE TEMPERA
@@ -7017,93 +6588,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>2024-03-23</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R59" t="n">
+      <c r="R60" t="n">
         <v>3107</v>
       </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="n">
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="n">
         <v>3107</v>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>3107.00000000</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
+    <row r="61">
+      <c r="A61" s="1" t="n">
         <v>45370</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>4951</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>8787</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA - ME</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>ASSISTENCIA TECNICA EXTERNA</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>194 - FORJAS CAXIENSE LTDA</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 FORJA MANUEL 3 UNIDADES
@@ -7124,93 +6685,83 @@
 QTD.: 1.000,000 KM</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>2024-03-22</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R60" t="n">
+      <c r="R61" t="n">
         <v>8028</v>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="n">
         <v>8028</v>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>8028.00000000</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
+    <row r="62">
+      <c r="A62" s="1" t="n">
         <v>45364</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>4922</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>8894</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>COMPRA DE PRODUTO</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>1047 - METALTECNICA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 ORCAMENTO PECAS DE REPOSICAO PARA MAQUINA TRATAMENTO TERMICO 017 NUMERO DE SERIE 10680-52
@@ -7225,93 +6776,87 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>2024-03-28</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>MICHAEL CRISTIANO CORREA</t>
         </is>
       </c>
-      <c r="R61" t="n">
+      <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>11673.72000000</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="n">
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="n">
         <v>11673.72</v>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>11673.72000000</t>
-        </is>
-      </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
+    <row r="63">
+      <c r="A63" s="1" t="n">
         <v>45359</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>4906</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>8812</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>193 - FORJAFIX ELEMENTOS DE FIXACAO LTDA</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>193 - FORJAFIX ELEMENTOS DE FIXACAO LTDA</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO INDUCAO ALIMENTACAO AUTOMATICA - 160KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -7341,105 +6886,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>2024-03-11</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
         <is>
           <t>4218-1</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R62" t="n">
+      <c r="R63" t="n">
         <v>4968.5</v>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>5942.14000000</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="n">
         <v>10910.64</v>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>10910.65000000</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
+    <row r="64">
+      <c r="A64" s="1" t="n">
         <v>45345</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>4839</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>5206</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>107 - WMOLDES EQUIPAMENTOS PARA INDUSTRIA VIDREIRA LTDA</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO MANUAL 40KW - 380V - FABRICACAO 3MI
@@ -7456,93 +6991,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>2024-02-25</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R63" t="n">
+      <c r="R64" t="n">
         <v>4890</v>
       </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="n">
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="n">
         <v>4890</v>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>4890.00000000</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
+    <row r="65">
+      <c r="A65" s="1" t="n">
         <v>45324</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>4758</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>6231</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO DE AQUECIMENTO INDUTIVO PARA FORJA - POTENCIA 160KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -7568,105 +7093,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>2024-02-05</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
         <is>
           <t>3841-1</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R64" t="n">
+      <c r="R65" t="n">
         <v>7787.2</v>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>1759.00000000</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="n">
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="n">
         <v>9546.200000000001</v>
       </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>9603.37000000</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
+    <row r="66">
+      <c r="A66" s="1" t="n">
         <v>45301</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>4658</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>8443</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>198 - METALTORK INDUSTRIA E COMERCIO DE AUTO PECAS LIMITADA</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>198 - METALTORK INDUSTRIA E COMERCIO DE AUTO PECAS LIMITADA</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO FORJA ALIMENTACAO AUTOMATICA - 120KW FREQUENCIA 15-30KHZ 380V - MARCA 3MI
@@ -7684,105 +7199,95 @@
 QTD.: 2,000 PC</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
         <is>
           <t>3745-1</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R65" t="n">
+      <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>7500.00000000</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="n">
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="n">
         <v>7500</v>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>7500.00000000</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
+    <row r="67">
+      <c r="A67" s="1" t="n">
         <v>45181</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>4270</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>8109</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>1689 - BF COMERCIO E INDUSTRIA DE FERRO E ACO EIRELI</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM UM EQUIPAMENTO MARCA JAMO AQUECIMENTO CONTINUO DE FIO MAQUINA
@@ -7806,93 +7311,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R66" t="n">
+      <c r="R67" t="n">
         <v>6563.6</v>
       </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="n">
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="n">
         <v>6563.6</v>
       </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>6563.60000000</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
+    <row r="68">
+      <c r="A68" s="1" t="n">
         <v>45034</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>3756</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>7390</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>1444 - ALLENFIX COMERCIO DE PARAFUSOS E FIXACOES LTDA</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>1444 - ALLENFIX COMERCIO DE PARAFUSOS E FIXACOES LTDA</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM DOIS EQUIPAMENTOS DE AQUECIMENTO POR INDUCAO MARCA 3MI
@@ -7906,93 +7401,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R67" t="n">
+      <c r="R68" t="n">
         <v>8590</v>
       </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="n">
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="n">
         <v>8590</v>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>8590.00000000</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
+    <row r="69">
+      <c r="A69" s="1" t="n">
         <v>45034</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>3755</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>7401</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>1546 - ALF INDUSTRIA E COMERCIO DE FIXADORES LTDA</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 SUBSTITUIR O FRONTAL GERAL DO TRANSFORMADOR MAQUINA 100KW -15-30KHZ FORJA MARCA 3MI POIS O MESMO ESTA BASTANTE AVARIADO
@@ -8009,101 +7494,91 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>2023-04-21</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
         <is>
           <t>3495-1</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R68" t="n">
+      <c r="R69" t="n">
         <v>720</v>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>1961.75000000</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="n">
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="n">
         <v>2681.75</v>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>2681.75000000</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
+    <row r="70">
+      <c r="A70" s="1" t="n">
         <v>44903</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SC</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>3397</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>12.563.613/0002-05</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
         <is>
           <t>4556 - INNIO JEANBACKER MOTORES A GAS LTDA.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>FABRICACAO DE EQUIPAMENTO NOVO</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>4556 - JEANBACKER MOTORES A GAS LTDA.</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>FORNECER 01 AQUECEDOR PARA SACAR SEDE DE VALVULAS 
 25KW - FREQUENCIA 15-30KHZ - 380V
@@ -8118,101 +7593,91 @@
 -GARANTIA EXTENDIDA 24 MESES, ONDE APÓS O START DO EQUIPAMENTO A CADA 6 MESES DEVEREMOS FAZER UMA MANUTENÇÃO PREVENTIVA NO CLIENTE.</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
         <is>
           <t>Produzido: 11651 (10895-14)</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>3412-1</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="n">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>117000.00000000</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="n">
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="n">
         <v>117000</v>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>117000.00000000</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
+    <row r="71">
+      <c r="A71" s="1" t="n">
         <v>44837</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>3228</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>6539</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>3302 - ORUOM IND.COM.PROD.METAL.INDUS.P/TERCEIROS LTDA</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO MANUAL - 25KW FREQUENCIA 15-30KHZ 380V - MARCA JAMO SERIE E05911
@@ -8227,93 +7692,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>2022-10-05</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R70" t="n">
+      <c r="R71" t="n">
         <v>3911</v>
       </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="n">
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="n">
         <v>3911</v>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>3911.00000000</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
+    <row r="72">
+      <c r="A72" s="1" t="n">
         <v>44837</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>3226</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>6694</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>598 - METALPRIME USINAGEM / ORION</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>598 - METALPRIME USINAGEM SERIADA EIRELI</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO TRATAMENTO TERMICO 
@@ -8330,93 +7785,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>2022-10-06</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R71" t="n">
+      <c r="R72" t="n">
         <v>7540</v>
       </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="n">
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="n">
         <v>7540</v>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>7540.00000000</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
+    <row r="73">
+      <c r="A73" s="1" t="n">
         <v>44750</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>2992</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>6403</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE FORJA 100KW TENSAO 380V FREQUENCIA 15-30KHZ
@@ -8447,105 +7892,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>2022-07-09</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
         <is>
           <t>2609-1</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R72" t="n">
+      <c r="R73" t="n">
         <v>1350.2</v>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>8366.86000000</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="n">
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="n">
         <v>9717.059999999999</v>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>9717.06000000</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
+    <row r="74">
+      <c r="A74" s="1" t="n">
         <v>44722</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>2904</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>5745</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>1076 - TMR INDUSTRIA E COMERCIO DE AUTO PECAS EIRELI ME</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO TEMPERA POR INDUCAO - 60KW FREQUENCIA 15-30KHZ 380V - MARCA 3MI
@@ -8561,93 +7996,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>2022-06-17</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R73" t="n">
+      <c r="R74" t="n">
         <v>5200</v>
       </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="n">
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="n">
         <v>5200</v>
       </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>5200.00000000</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
+    <row r="75">
+      <c r="A75" s="1" t="n">
         <v>44720</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>2893</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>6328</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO MANUAL FORJA 120KW FREQUENCIA 15-30KHZ - 380V
@@ -8680,105 +8105,95 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>2022-06-09</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
         <is>
           <t>2579-1</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R74" t="n">
+      <c r="R75" t="n">
         <v>2836.6</v>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>2218.84000000</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="n">
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="n">
         <v>5055.44</v>
       </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>5055.46000000</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
+    <row r="76">
+      <c r="A76" s="1" t="n">
         <v>44719</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>2887</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>6299</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>2846 - MHT INDUSTRIA E COMERCIO DE COMPONENTES AUTOMOTIVOS LTDA</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>2846 - MHT INDUSTRIA E COMERCIO DE COMPONENTES AUTOMOTIVOS LTDA</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO INDUTIVO FORJA ALIMENTACAO PNEUMATICO COM CALHA 120KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -8792,93 +8207,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>2022-06-10</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R75" t="n">
+      <c r="R76" t="n">
         <v>4890</v>
       </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="n">
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="n">
         <v>4890</v>
       </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>4890.00000000</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
+    <row r="77">
+      <c r="A77" s="1" t="n">
         <v>44708</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>2847</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>6274</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO MANUAL FORJA 120KW FREQUENCIA 15-30KHZ - 380V
@@ -8911,105 +8316,95 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>2022-05-28</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
         <is>
           <t>2563-1</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R76" t="n">
+      <c r="R77" t="n">
         <v>2639.2</v>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>1633.42000000</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="n">
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="n">
         <v>4272.62</v>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>4272.63000000</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
+    <row r="78">
+      <c r="A78" s="1" t="n">
         <v>44691</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>6204</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FORJA AQUECIMENTO INDUTIVO MANUAL - 100KW FREQUENCIA 15-30KHZ TENSAO 380V
@@ -9041,105 +8436,95 @@
 QTD.: 3,000 M</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>2022-05-12</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
         <is>
           <t>2548-1</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R77" t="n">
+      <c r="R78" t="n">
         <v>3780.8</v>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>2757.50000000</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="n">
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="n">
         <v>6538.3</v>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>6538.31000000</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
+    <row r="79">
+      <c r="A79" s="1" t="n">
         <v>44662</v>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>2714</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>5965</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>2674 - ROAPLAS PLASTICOS E FERRAGENS LTDA.</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO AQUECIMENTO INDUTIVO ALIMENTACAO PNEUMATICO - 40KW 380V FREQUENCIA 15-30KHZ
@@ -9150,93 +8535,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>2022-04-16</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R78" t="n">
+      <c r="R79" t="n">
         <v>4230</v>
       </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="n">
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="n">
         <v>4230</v>
       </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>4230.00000000</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
+    <row r="80">
+      <c r="A80" s="1" t="n">
         <v>44645</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>2666</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>6078</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>1085 - BRASIMPAR INDUSTRIA METALURGICA EIRELI</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO EM DOIS EQUIPAMENTO FORJARIA 10 E 40KW
@@ -9257,105 +8632,95 @@
 QTD.: 2,000 UN</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>2022-03-26</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
         <is>
           <t>2499-1</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R79" t="n">
+      <c r="R80" t="n">
         <v>838.8</v>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>2164.23000000</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="n">
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="n">
         <v>3003.03</v>
       </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>3003.03000000</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
+    <row r="81">
+      <c r="A81" s="1" t="n">
         <v>44397</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>1948</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>5194</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>1425 - ZL BRASIL</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>1425 - ZUCOLLO AUTO PARTS IND COM EXP IMP LTDA</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO TEMPERA POR INDUCAO AQUECIMENTO DUPLO - 160KW - 380V FABRICACAO 3MI
@@ -9370,89 +8735,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>2021-07-23</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R80" t="n">
+      <c r="R81" t="n">
         <v>4820</v>
       </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="n">
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="n">
         <v>4820</v>
       </c>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>4820.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
+    <row r="82">
+      <c r="A82" s="1" t="n">
         <v>44397</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>1944</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>5349</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA E METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>717 - FORTE FIXADORES INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO FABRICACAO 3MI ALIMENTACAO MANUAL - 100KW - 380V - FREQUENCIA DE TRABALHO 15-30KHZ
@@ -9464,93 +8823,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>2021-07-22</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
         <is>
           <t>SERGIO PRATES PEREIRA</t>
         </is>
       </c>
-      <c r="R81" t="n">
+      <c r="R82" t="n">
         <v>3800</v>
       </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="n">
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="n">
         <v>3800</v>
       </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>3800.00000000</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
+    <row r="83">
+      <c r="A83" s="1" t="n">
         <v>44368</v>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>1887</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>5301</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>2385 - FORJARIA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 EQUIPAMENTO DE FORJARIA ALIMENTACAO PNEUMATICA E CALHA 120KW
@@ -9566,93 +8915,83 @@
 QTD.: 1,000 UN</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>2021-06-23</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R82" t="n">
+      <c r="R83" t="n">
         <v>4600</v>
       </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="n">
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="n">
         <v>4600</v>
       </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>4600.00000000</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
-      </c>
     </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
+    <row r="84">
+      <c r="A84" s="1" t="n">
         <v>44334</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>3MI INDUCAO - SP</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>1793</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>3MI INDUSTRIA E COMERCIO DE MAQUINAS E EQUIPAMENTOS INDUSTRI</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>&lt;img src="../../_img/realizado.png" data-title="OK" width="16px" height="16px" /&gt;</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>12.563.613/0001-16</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>5193</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>SP - ASSISTENCIA TECNICA</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>180 - METALURGICA DELLA ROSA LTDA</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>FINALIZADO</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>EQUIPAMENTO:
 MANUTENCAO PREVENTIVA EM EQUIPAMENTO AQUECIMENTO DUPLO 160KW DE FABRICACAO 3MI
@@ -9668,36 +9007,26 @@
 QTD.: 1,000 PC</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>2021-05-21</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
         <is>
           <t>GIOVANI ZAVADIL</t>
         </is>
       </c>
-      <c r="R83" t="n">
+      <c r="R84" t="n">
         <v>4600</v>
       </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="n">
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="n">
         <v>4600</v>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>4600.00000000</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>0.00000000</t>
-        </is>
       </c>
     </row>
   </sheetData>
